--- a/conception_Login_TestCases.xlsx
+++ b/conception_Login_TestCases.xlsx
@@ -331,7 +331,7 @@
     <t>LOGIN-08</t>
   </si>
   <si>
-    <t>Vérifier la présence du bouton Log out</t>
+    <t xml:space="preserve">Vérifier la présence du bouton Log out </t>
   </si>
   <si>
     <t>Le bouton Log out est visible après une connexion réussie.</t>
@@ -440,7 +440,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -453,6 +453,11 @@
     </font>
     <font>
       <color rgb="FF000000"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color rgb="FF7F7F7F"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -484,17 +489,25 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -515,6 +528,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -45378,7 +45392,7 @@
     </row>
   </sheetData>
   <autoFilter ref="$A$1:$P$13"/>
-  <dataValidations count="6">
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" sqref="E2:E23">
       <formula1>"MEDIUM,HIGH"</formula1>
     </dataValidation>
@@ -45386,9 +45400,6 @@
       <formula1>"Test système,Transition d'état"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="L8">
-      <formula1>"Prévu,Non"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="M10:M23">
       <formula1>"Prévu,Non"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="M2:M7">
@@ -45489,15 +45500,15 @@
     <row r="7" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
+      <c r="C7" s="10"/>
       <c r="D7" s="2"/>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="11" t="s">
         <v>135</v>
       </c>
       <c r="H7" s="2"/>
@@ -45507,13 +45518,13 @@
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="11" t="s">
         <v>137</v>
       </c>
       <c r="H8" s="2"/>
@@ -45523,13 +45534,13 @@
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="11" t="s">
         <v>139</v>
       </c>
       <c r="H9" s="2"/>

--- a/conception_Login_TestCases.xlsx
+++ b/conception_Login_TestCases.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="134">
   <si>
     <t>ID</t>
   </si>
@@ -49,34 +49,28 @@
     <t>RM-05</t>
   </si>
   <si>
-    <t>Une connexion réussie redirige vers la page de succès.</t>
+    <t>Après une connexion réussie, l'URL contient « logged-in-successfully/ ».</t>
   </si>
   <si>
     <t>RM-06</t>
   </si>
   <si>
-    <t>Après une connexion réussie, l'URL contient « logged-in-successfully/ ».</t>
+    <t>Après une connexion réussie, un message de confirmation est affiché.</t>
   </si>
   <si>
     <t>RM-07</t>
   </si>
   <si>
-    <t>Après une connexion réussie, un message de confirmation est affiché.</t>
+    <t>Après une connexion réussie, le bouton « Log out » est affiché.</t>
   </si>
   <si>
     <t>RM-08</t>
   </si>
   <si>
-    <t>Après une connexion réussie, le bouton « Log out » est affiché.</t>
+    <t>Une erreur de Username affiche le message « Your username is invalid! ».</t>
   </si>
   <si>
     <t>RM-09</t>
-  </si>
-  <si>
-    <t>Une erreur de Username affiche le message « Your username is invalid! ».</t>
-  </si>
-  <si>
-    <t>RM-10</t>
   </si>
   <si>
     <t>Une erreur de Password affiche le message « Your password is invalid! ».</t>
@@ -265,7 +259,7 @@
     <t>LOGIN-04</t>
   </si>
   <si>
-    <t>Se connecter avec des identifiants valides</t>
+    <t>Vérifier l'URL après une connexion réussie suite à une  connection avec des identifiants valides</t>
   </si>
   <si>
     <t>RM-01, RM-02, RM-05</t>
@@ -274,7 +268,7 @@
     <t>HIGH</t>
   </si>
   <si>
-    <t>Un utilisateur saisit les identifiants valides et clique sur Submit.</t>
+    <t>Un utilisateur saisit les identifiants valides et clique sur Submit. Après une connexion réussie, l'URL de la page de succès est correcte.</t>
   </si>
   <si>
     <t>Test basé sur les cas d'utilisation</t>
@@ -286,25 +280,10 @@
     <t>Username : student ; Password : Password123</t>
   </si>
   <si>
-    <t>La connexion réussit et l'utilisateur est redirigé vers la page de succès.</t>
+    <t>La connexion réussit et l'utilisateur est redirigé vers la page de succès. L'URL contient « /logged-in-successfully/ ».</t>
   </si>
   <si>
     <t>LOGIN-05</t>
-  </si>
-  <si>
-    <t>Vérifier l'URL après une connexion réussie</t>
-  </si>
-  <si>
-    <t>Après une connexion réussie, l'URL de la page de succès est correcte.</t>
-  </si>
-  <si>
-    <t>PRE-01, PRE-02, PRE-03</t>
-  </si>
-  <si>
-    <t>L'URL contient « practicetestautomation.com/logged-in-successfully/ ».</t>
-  </si>
-  <si>
-    <t>LOGIN-06</t>
   </si>
   <si>
     <t>Vérifier le message « Logged In Successfully »</t>
@@ -313,10 +292,13 @@
     <t>Un message confirme la réussite de la connexion.</t>
   </si>
   <si>
+    <t>PRE-01, PRE-02, PRE-03</t>
+  </si>
+  <si>
     <t>Le texte « Logged In Successfully » est affiché.</t>
   </si>
   <si>
-    <t>LOGIN-07</t>
+    <t>LOGIN-06</t>
   </si>
   <si>
     <t>Vérifier le message de félicitations après connexion</t>
@@ -328,7 +310,7 @@
     <t>Le texte « Congratulations student. You successfully logged in » est affiché.</t>
   </si>
   <si>
-    <t>LOGIN-08</t>
+    <t>LOGIN-07</t>
   </si>
   <si>
     <t xml:space="preserve">Vérifier la présence du bouton Log out </t>
@@ -340,7 +322,7 @@
     <t>Le bouton « Log out » est visible.</t>
   </si>
   <si>
-    <t>LOGIN-09</t>
+    <t>LOGIN-08</t>
   </si>
   <si>
     <t>Se connecter avec un nom d'utilisateur incorrect</t>
@@ -361,7 +343,7 @@
     <t>La connexion échoue et le message « Your username is invalid! » est affiché.</t>
   </si>
   <si>
-    <t>LOGIN-10</t>
+    <t>LOGIN-09</t>
   </si>
   <si>
     <t>Se connecter avec un mot de passe incorrect</t>
@@ -379,7 +361,7 @@
     <t>La connexion échoue et le message « Your password is invalid! » est affiché.</t>
   </si>
   <si>
-    <t>LOGIN-11</t>
+    <t>LOGIN-10</t>
   </si>
   <si>
     <t>Vérifier l'échec de connexion avec un Username incorrect</t>
@@ -394,7 +376,7 @@
     <t>L'utilisateur reste sur la page de connexion et la page de succès n'est pas affichée.</t>
   </si>
   <si>
-    <t>LOGIN-12</t>
+    <t>LOGIN-11</t>
   </si>
   <si>
     <t>Vérifier l'échec de connexion avec un Password incorrect</t>
@@ -871,7 +853,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F1000"/>
+  <dimension ref="A1:F999"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12.571428571428571" customWidth="1"/>
@@ -896,7 +878,7 @@
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="2"/>
@@ -908,7 +890,7 @@
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="2"/>
@@ -920,7 +902,7 @@
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2"/>
@@ -932,7 +914,7 @@
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="2"/>
@@ -944,7 +926,7 @@
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="2"/>
@@ -956,7 +938,7 @@
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="2"/>
@@ -968,7 +950,7 @@
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C8" s="2"/>
@@ -980,7 +962,7 @@
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C9" s="2"/>
@@ -992,7 +974,7 @@
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C10" s="2"/>
@@ -1000,13 +982,9 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
     </row>
-    <row r="11" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>21</v>
-      </c>
+    <row r="11" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -8915,14 +8893,6 @@
       <c r="D999" s="2"/>
       <c r="E999" s="2"/>
       <c r="F999" s="2"/>
-    </row>
-    <row r="1000" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1000" s="2"/>
-      <c r="B1000" s="2"/>
-      <c r="C1000" s="2"/>
-      <c r="D1000" s="2"/>
-      <c r="E1000" s="2"/>
-      <c r="F1000" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8948,85 +8918,85 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F1" s="4"/>
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="3" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="B4" s="3" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="4" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>33</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="B5" s="3" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="5" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="B6" s="3" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="6" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -9035,10 +9005,10 @@
     </row>
     <row r="7" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -9047,10 +9017,10 @@
     </row>
     <row r="8" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -17001,7 +16971,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z1000"/>
+  <dimension ref="A1:Z999"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -17025,52 +16995,52 @@
   <sheetData>
     <row r="1" ht="33" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>59</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>61</v>
       </c>
       <c r="Q1" s="6"/>
       <c r="R1" s="6"/>
@@ -17085,47 +17055,47 @@
     </row>
     <row r="2" ht="78" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="E2" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="F2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="H2" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G2" s="7" t="s">
+      <c r="I2" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="J2" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="L2" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="K2" s="7" t="s">
+      <c r="M2" s="7" t="s">
         <v>70</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>72</v>
       </c>
       <c r="N2" s="7"/>
       <c r="O2" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="P2" s="7"/>
       <c r="Q2" s="6"/>
@@ -17141,47 +17111,47 @@
     </row>
     <row r="3" ht="78" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="E3" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="L3" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" s="8" t="s">
+      <c r="M3" s="8" t="s">
         <v>70</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="M3" s="8" t="s">
-        <v>72</v>
       </c>
       <c r="N3" s="8"/>
       <c r="O3" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="P3" s="8"/>
       <c r="Q3" s="6"/>
@@ -17197,47 +17167,47 @@
     </row>
     <row r="4" ht="78" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="G4" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="L4" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="K4" s="7" t="s">
+      <c r="M4" s="7" t="s">
         <v>70</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>72</v>
       </c>
       <c r="N4" s="7"/>
       <c r="O4" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="P4" s="7"/>
       <c r="Q4" s="6"/>
@@ -17253,47 +17223,47 @@
     </row>
     <row r="5" ht="78" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="E5" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="F5" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="G5" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="H5" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="J5" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="K5" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="H5" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="J5" s="8" t="s">
+      <c r="L5" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="K5" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>90</v>
-      </c>
       <c r="M5" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="N5" s="8"/>
       <c r="O5" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="P5" s="8"/>
       <c r="Q5" s="6"/>
@@ -17308,50 +17278,50 @@
       <c r="Z5" s="6"/>
     </row>
     <row r="6" ht="78" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>62</v>
+      <c r="A6" s="8" t="s">
+        <v>60</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="G6" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="J6" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>12</v>
+      <c r="K6" s="8" t="s">
+        <v>87</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="F6" s="7" t="s">
+      <c r="L6" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="G6" s="7" t="s">
-        <v>67</v>
+      <c r="M6" s="8" t="s">
+        <v>70</v>
       </c>
-      <c r="H6" s="7" t="s">
-        <v>68</v>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8" t="s">
+        <v>71</v>
       </c>
-      <c r="I6" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="P6" s="7"/>
+      <c r="P6" s="8"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
       <c r="S6" s="6"/>
@@ -17364,50 +17334,49 @@
       <c r="Z6" s="6"/>
     </row>
     <row r="7" ht="78" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>62</v>
+      <c r="A7" s="7" t="s">
+        <v>60</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="G7" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="L7" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>14</v>
+      <c r="M7" s="7" t="s">
+        <v>70</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>85</v>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7" t="s">
+        <v>71</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="P7" s="8"/>
       <c r="Q7" s="6"/>
       <c r="R7" s="6"/>
       <c r="S7" s="6"/>
@@ -17420,49 +17389,50 @@
       <c r="Z7" s="6"/>
     </row>
     <row r="8" ht="78" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>62</v>
+      <c r="A8" s="8" t="s">
+        <v>60</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="G8" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="L8" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>14</v>
+      <c r="M8" s="8" t="s">
+        <v>70</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>66</v>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8" t="s">
+        <v>71</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7" t="s">
-        <v>73</v>
-      </c>
+      <c r="P8" s="8"/>
       <c r="Q8" s="6"/>
       <c r="R8" s="6"/>
       <c r="S8" s="6"/>
@@ -17475,50 +17445,50 @@
       <c r="Z8" s="6"/>
     </row>
     <row r="9" ht="78" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
-        <v>62</v>
+      <c r="A9" s="7" t="s">
+        <v>60</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="E9" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>16</v>
+      <c r="G9" s="7" t="s">
+        <v>85</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="H9" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="I9" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="J9" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="G9" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="L9" s="8" t="s">
+      <c r="K9" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="M9" s="8" t="s">
-        <v>72</v>
+      <c r="L9" s="7" t="s">
+        <v>108</v>
       </c>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8" t="s">
-        <v>73</v>
+      <c r="M9" s="7" t="s">
+        <v>70</v>
       </c>
-      <c r="P9" s="8"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="P9" s="7"/>
       <c r="Q9" s="6"/>
       <c r="R9" s="6"/>
       <c r="S9" s="6"/>
@@ -17531,50 +17501,50 @@
       <c r="Z9" s="6"/>
     </row>
     <row r="10" ht="78" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>62</v>
+      <c r="A10" s="8" t="s">
+        <v>60</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="C10" s="7" t="s">
+      <c r="B10" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="D10" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>111</v>
+      <c r="H10" s="8" t="s">
+        <v>66</v>
       </c>
-      <c r="G10" s="7" t="s">
-        <v>87</v>
+      <c r="I10" s="8" t="s">
+        <v>67</v>
       </c>
-      <c r="H10" s="7" t="s">
-        <v>68</v>
+      <c r="J10" s="8" t="s">
+        <v>106</v>
       </c>
-      <c r="I10" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="K10" s="7" t="s">
+      <c r="K10" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="L10" s="7" t="s">
+      <c r="L10" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="M10" s="7" t="s">
-        <v>72</v>
+      <c r="M10" s="8" t="s">
+        <v>70</v>
       </c>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7" t="s">
-        <v>73</v>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8" t="s">
+        <v>71</v>
       </c>
-      <c r="P10" s="7"/>
+      <c r="P10" s="8"/>
       <c r="Q10" s="6"/>
       <c r="R10" s="6"/>
       <c r="S10" s="6"/>
@@ -17587,50 +17557,50 @@
       <c r="Z10" s="6"/>
     </row>
     <row r="11" ht="78" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>62</v>
+      <c r="A11" s="7" t="s">
+        <v>60</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="E11" s="8" t="s">
-        <v>85</v>
+      <c r="G11" s="7" t="s">
+        <v>65</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="H11" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="J11" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="G11" s="8" t="s">
-        <v>87</v>
+      <c r="K11" s="7" t="s">
+        <v>107</v>
       </c>
-      <c r="H11" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K11" s="8" t="s">
+      <c r="L11" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="L11" s="8" t="s">
-        <v>120</v>
+      <c r="M11" s="7" t="s">
+        <v>70</v>
       </c>
-      <c r="M11" s="8" t="s">
-        <v>72</v>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7" t="s">
+        <v>71</v>
       </c>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="P11" s="8"/>
+      <c r="P11" s="7"/>
       <c r="Q11" s="6"/>
       <c r="R11" s="6"/>
       <c r="S11" s="6"/>
@@ -17643,50 +17613,50 @@
       <c r="Z11" s="6"/>
     </row>
     <row r="12" ht="78" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>62</v>
+      <c r="A12" s="8" t="s">
+        <v>60</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="D12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F12" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>6</v>
+      <c r="G12" s="8" t="s">
+        <v>65</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="H12" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="F12" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="G12" s="7" t="s">
+      <c r="I12" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="H12" s="7" t="s">
-        <v>68</v>
+      <c r="J12" s="8" t="s">
+        <v>118</v>
       </c>
-      <c r="I12" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="K12" s="7" t="s">
+      <c r="K12" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="L12" s="7" t="s">
-        <v>125</v>
+      <c r="L12" s="8" t="s">
+        <v>119</v>
       </c>
-      <c r="M12" s="7" t="s">
-        <v>72</v>
+      <c r="M12" s="8" t="s">
+        <v>70</v>
       </c>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7" t="s">
-        <v>73</v>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8" t="s">
+        <v>71</v>
       </c>
-      <c r="P12" s="7"/>
+      <c r="P12" s="8"/>
       <c r="Q12" s="6"/>
       <c r="R12" s="6"/>
       <c r="S12" s="6"/>
@@ -17698,51 +17668,23 @@
       <c r="Y12" s="6"/>
       <c r="Z12" s="6"/>
     </row>
-    <row r="13" ht="78" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="K13" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="M13" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="N13" s="8"/>
-      <c r="O13" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="P13" s="8"/>
+    <row r="13" ht="15.75" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
       <c r="Q13" s="6"/>
       <c r="R13" s="6"/>
       <c r="S13" s="6"/>
@@ -17755,22 +17697,22 @@
       <c r="Z13" s="6"/>
     </row>
     <row r="14" ht="15.75" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
-      <c r="P14" s="7"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
       <c r="S14" s="6"/>
@@ -17783,22 +17725,22 @@
       <c r="Z14" s="6"/>
     </row>
     <row r="15" ht="15.75" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8"/>
-      <c r="O15" s="8"/>
-      <c r="P15" s="8"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
       <c r="Q15" s="6"/>
       <c r="R15" s="6"/>
       <c r="S15" s="6"/>
@@ -17811,22 +17753,22 @@
       <c r="Z15" s="6"/>
     </row>
     <row r="16" ht="15.75" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
       <c r="Q16" s="6"/>
       <c r="R16" s="6"/>
       <c r="S16" s="6"/>
@@ -17839,22 +17781,22 @@
       <c r="Z16" s="6"/>
     </row>
     <row r="17" ht="15.75" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="8"/>
-      <c r="P17" s="8"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
       <c r="Q17" s="6"/>
       <c r="R17" s="6"/>
       <c r="S17" s="6"/>
@@ -17867,22 +17809,22 @@
       <c r="Z17" s="6"/>
     </row>
     <row r="18" ht="15.75" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="7"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="8"/>
       <c r="Q18" s="6"/>
       <c r="R18" s="6"/>
       <c r="S18" s="6"/>
@@ -17895,22 +17837,22 @@
       <c r="Z18" s="6"/>
     </row>
     <row r="19" ht="15.75" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
-      <c r="N19" s="8"/>
-      <c r="O19" s="8"/>
-      <c r="P19" s="8"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="7"/>
       <c r="Q19" s="6"/>
       <c r="R19" s="6"/>
       <c r="S19" s="6"/>
@@ -17923,22 +17865,22 @@
       <c r="Z19" s="6"/>
     </row>
     <row r="20" ht="15.75" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
-      <c r="P20" s="7"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="8"/>
       <c r="Q20" s="6"/>
       <c r="R20" s="6"/>
       <c r="S20" s="6"/>
@@ -17951,22 +17893,22 @@
       <c r="Z20" s="6"/>
     </row>
     <row r="21" ht="15.75" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8"/>
-      <c r="O21" s="8"/>
-      <c r="P21" s="8"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
+      <c r="O21" s="7"/>
+      <c r="P21" s="7"/>
       <c r="Q21" s="6"/>
       <c r="R21" s="6"/>
       <c r="S21" s="6"/>
@@ -17979,22 +17921,22 @@
       <c r="Z21" s="6"/>
     </row>
     <row r="22" ht="15.75" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
-      <c r="P22" s="7"/>
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="8"/>
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
       <c r="S22" s="6"/>
@@ -18007,22 +17949,22 @@
       <c r="Z22" s="6"/>
     </row>
     <row r="23" ht="15.75" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8"/>
-      <c r="L23" s="8"/>
-      <c r="M23" s="8"/>
-      <c r="N23" s="8"/>
-      <c r="O23" s="8"/>
-      <c r="P23" s="8"/>
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
+      <c r="O23" s="7"/>
+      <c r="P23" s="7"/>
       <c r="Q23" s="6"/>
       <c r="R23" s="6"/>
       <c r="S23" s="6"/>
@@ -45361,34 +45303,6 @@
       <c r="X999" s="6"/>
       <c r="Y999" s="6"/>
       <c r="Z999" s="6"/>
-    </row>
-    <row r="1000" ht="15.75" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A1000" s="7"/>
-      <c r="B1000" s="7"/>
-      <c r="C1000" s="7"/>
-      <c r="D1000" s="7"/>
-      <c r="E1000" s="7"/>
-      <c r="F1000" s="7"/>
-      <c r="G1000" s="7"/>
-      <c r="H1000" s="7"/>
-      <c r="I1000" s="7"/>
-      <c r="J1000" s="7"/>
-      <c r="K1000" s="7"/>
-      <c r="L1000" s="7"/>
-      <c r="M1000" s="7"/>
-      <c r="N1000" s="7"/>
-      <c r="O1000" s="7"/>
-      <c r="P1000" s="7"/>
-      <c r="Q1000" s="6"/>
-      <c r="R1000" s="6"/>
-      <c r="S1000" s="6"/>
-      <c r="T1000" s="6"/>
-      <c r="U1000" s="6"/>
-      <c r="V1000" s="6"/>
-      <c r="W1000" s="6"/>
-      <c r="X1000" s="6"/>
-      <c r="Y1000" s="6"/>
-      <c r="Z1000" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="$A$1:$P$13"/>
@@ -45475,7 +45389,7 @@
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="9" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -45487,13 +45401,13 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="1" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H6" s="2"/>
     </row>
@@ -45503,13 +45417,13 @@
       <c r="C7" s="10"/>
       <c r="D7" s="2"/>
       <c r="E7" s="11" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="H7" s="2"/>
     </row>
@@ -45519,13 +45433,13 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="11" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="H8" s="2"/>
     </row>
@@ -45535,13 +45449,13 @@
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="11" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="H9" s="2"/>
     </row>
